--- a/data/MBBS_IN_OTHER_STATE.xlsx
+++ b/data/MBBS_IN_OTHER_STATE.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="MBBS Cutoff 2025" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="MBBS Cutoff 2025" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -22,594 +29,1393 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="154">
   <si>
-    <t xml:space="preserve">College Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIR 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jubilee Mission Medical College &amp; Research Institute, Thrissur (Christian Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kerala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amala Institute of Medical Sciences, Thrissur (Christian Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pushpagiri Institute Of Medical Sciences and Research Centre, Tiruvalla (Christian Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malankara Orthodox Syrian Church Medical College, Kolenchery (Christian Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al-Ameen Medical College, Bijapur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karnataka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sree Gokulam Medical College Trust &amp; Research Foundation, Trivandrum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Believers Church Medical College Hospital, Thiruvalla, Kerala (Christian Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kempegowda Institute of Medical Sciences, Bangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vydehi Institute of Medical Science and Research Centre, Bangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Father Muller Institute of Med. Education &amp; Research, Mangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M E S Medical College , Perintalmanna Malappuram Distt (Muslim Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMCT Medical College, Kozhikode, Calicut (Muslim Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travancore Medical College, Mylapore, Umayanalloor P O, Kollam (Muslim Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Somervel Memorial CSI Hospital &amp; Medical College, Karakonam, Thiruvananthapuram (Christian Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sree Narayana Instt. of Medical Sciences, Chalakka, Ernakulam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUT Sree Uthradom Thiurnal Academy of Medical Sciences, Trivandrum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BGS MEDICAL COLLAGE AND HOSPITAL,BANGALURU (Private-University)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raipur Institute of Medical Sciences (RIMS), Raipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chhattisgarh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. B.R. Ambedkar Medical College, Bangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Moopens Medical College ,Meppadi P.O., Wayanad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaya Jagadguru Murugharajendra Medical College, Davangere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.J.Institute of Medical Sciences &amp; Research Center, Mangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.V.J.Medical College and Research Hospital, Bangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P K Das Institute of Medical Sciences, Palakkad, Kerala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karuna Medical College, Palakkad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shymanuru Shivashankarappa Institute Of Medical Sciences, Davangere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mount Zion Medical College, Chayalode, Ezhamkulam Adoor, Pathanamthitta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appolo Institute of Medical Sciences and Research, Hyderabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telangana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palakkad Institute of Medical Sciences, Palakkad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akash Institute of Medical Sciences &amp; Research centre, Banglore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Oxford Medical College, Hospital &amp; Research Centre, Bangalore,(Linguistic Telugu )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al-Azhar Medical College and Super Speciality Hospital, Thodupuzha (Muslim Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shri Balaji Institute of Medical Science, Raipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahadevappa Rampure Medical College, Gulbarga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">East Point College of Medical Sciences and Research Center, Bangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIDDAGANGA MEDICAL COLLEGE AND RESEARCH INSTITUTE,,TUMAKURU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deccan College of Medical Sciences, Hyderabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S. Nijalingappa Medical College and Research Centre, Bagalkot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mamata Academy of Medical Sciences, Bachupally</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamineni Academy of Medical Sciences &amp; Research Centre, Hyderabad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bhaskar Medical College, Yenkapally,Hyderabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basaveshwara Medical College and Hospital, Chitradurga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadan Institute of Medical Sciences, Research Centre &amp;Teaching Hospital, Peerancheru, Hyderabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navodaya Medical College, Raichur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S R PATIL MEDICAL COLLEGE HOSPITAL AND RESEARCH CENTER,BADAGANDI,BAGALKOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subbaiah Institute of Medical Science, shimoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRI CHAMUNDESHWARI MEDICAL COLLEGE, HOSPITAL AND RESEARCH INST,,CHANNAPATNA, RAMANAGARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.S.Ramaiah Medical College, Bangalore (Private-University)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abhishek I Mishra Memorial Medical College &amp; Research, Bhiali, Durg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SVS Medical College, Mehaboobnagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shridevi Institute of Medical Sciences &amp; Research Hospital, Tumkur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanachur Institute of Medical Sciences and Research Centre, Mangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mamata Medical College, Khammam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mediciti Institute of Medical Sciences, Ghanpur,Hyderabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maheswara Medical College, Chitkul, Patancheru, Medak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K.Venkataramana Gowda Medical College and Hospital, Mangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prathima Institute of Medical Sciences, Karimnagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RVM Institute of Medical sciences and Research Centre, Medak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shri Rawatpura Sarkar Institute of Medical Sciences and Research, Nava Raipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahavir Institute Of Medical Sciences, Vikarabad, Telengana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K.D. Medical College Hospital &amp; Research Centre, Mathura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uttar Pradesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sri Madhusudan Sai Institute of Medical Sciences and Research, Chikballapur (Private-University)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamineni Institute of Medical Sciences, Narketpally.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDM College of Medical Sciences and Hospital, Dharwad (Private-University)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova inst. Hayathnagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khaja Bande Navaz Institute Of Medical Sciences, Gulbarga (Private-University)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pratima relif Warngal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRR INSTITUTE OF MEDICAL SCIENCES, INOLE, PATANCHERU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surabhi Institute of Medical Sciences, Siddipet, Telangana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FATHER COLOMBO INSTITUTE OF MEDICAL SCIENCES, WARANGAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Inst. Of Medical Science, Prayagraj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hind Institute of Medical Sciences, Barabanki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hind Institute of Medical Sciences, Sitapur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PES UNIVERSITY INSTITUTE OF MEDICAL SCIENCES AND RESEARCH,ELECTRONIC CITY,BANGALORE (Private-University)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heritage Institute of Medical Sciences, Varanasi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saraswati Institute of Medical Sciences, Hapur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">School of Medical Sciences &amp; Research ( Sharda University),Greater Noida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shri Gorakshnath Medical College, Hospital and Research Centre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chalmeda Anand Rao Institute of Medical Science, Karimnagar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNR Medical College &amp; Hospital, Sangareddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR. CHANDRAMMA DAYANANDA SAGAR INSTITUTE OF MEDICAL EDUCATION &amp; RESEARCH,HAROHALLI.(Private-University)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rama Medical College Hospital &amp; Research Centre, Hapur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adichunchanagiri Institute of Medical Sciences, Mandya (Private-University)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEELIMA INSTITUTE OF MEDICAL SCIENCES, GHATKESAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subharti Medical College, Meerut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rama Medical College &amp; Hospital , Kanpur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muzaffarnagar Medical College, Muzaffarnagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mayo Institute of Medical Sciences, Barabanki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Capital Reagon Int. Of Medical Sci.,Meerut (MSY Medical College)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G.S Medical College, Hapur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prasad Institute of Medical Sciences, Lucknow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S.K.S. HOSPITAL MATHURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sri Venkteshwara Inst.Of Medical Sci. Amroha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajay Sangaal Institute Of Medical Sciences &amp; Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narayana Medical College, Kanpur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krishna Mohan Medical College &amp; Hospital, Mathura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saraswati Medical College, Unnao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shri Shankaracharya Institute of Medical Sciences, Bhilai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr BS Kushwah Institute of Medical Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noida INternational Inst. Of Med. Sci,Gautam Budh Nagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shri RamMurti Smarak Institute of Medical Sciences, Bareilly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sapthagiri Institute of Medical Sciences, Bangalore (Private-University)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varunarjun Medical College, Sahjahanpur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMC Medical College &amp; Hospital Maharajganj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BGS Global Institute of Medical Sciences, Bangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rohilkhand Medical College &amp; Hospital, Bareilly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geetanjali Medical College &amp; Hospital,Udaipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rajasthan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Era Lucknow Medical College, Lucknow(Muslim Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Srinivasa Institute of Medical Research Center, Mangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T.S Mishra Medical College &amp; Hospital, Lucknow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rajshree Medical Research Institute, Barielly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integral Institute of Medical Sciences &amp; Research, Lucknow(Muslim Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F.H. Medical College &amp; Hospital, Firozabad, Agra(Muslim Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaipur National University Institute of Medical Sciences and Resarch Centre, Jagatpura, Jaipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ananta Institute of Medical Sciences &amp; Research Centre, Rajsamand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American International Institute of Medical Sciences, Bedwas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Institute of Medical Science &amp; Research, Jaipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teerthankar Mahaveer Medical College, Moradabad(Jain Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. S.S. Tantia Medical College, Hospital &amp; Research Centre Tantia University, Sri Ganganagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahatma Gandhi Medical College and Hospital, Jaipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sudha Medical College, Via Jagpura, Jhalawar Road, Kota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JIET Medical College And Hospital, Village Mogra, Jodhpur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacific Institute of Medical Sciences, Umarda, Udaipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vyas Medical College &amp; Hospital, Pali Road Jodhpu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacific Medical College &amp; Hospital, Bhilo Ka Bedla, Udaipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Career Institute of Medical Sciences &amp; hospital, Lucknow(Muslim Minority)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRI Medical College, Chinnakakani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andhra Pradesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narayana Medical College, Nellore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apollo Institute of Medical Sciences and Research, Chittoor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alluri Seetharama Raju Academy of Medical Sciences, Eluru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Pinnamaneni Siddhartha Institute of Medical Sciences, Gannavaram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSL Medical College, Rajahmundry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRI Institute of Medical Sciences, Visakhapatnam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katuri Medical College and Hospital, Guntur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P.E.S. Institute of Medical Sciences and Research, Kuppam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konasema Institute of Medical Sciences and Research Foundation, Amalapuram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Great Eastern Medical School and Hospital, Srikakulam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viswabharathi Medical College, Kurnool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sri Balaji Medical College Hospital &amp; Research Institute, Renigunta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gayatri Vidya Parishad Inst. of Health Care and Medical Technology, Visakhapatnam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santhiram Medical College, Nandyal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maharaja Institute of Medical Sciences, Vizianagaram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anna Gowri Medical College and Hospital, Parameshwaramangalam</t>
+    <t>College Name</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>AIR 2025</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>Jubilee Mission Medical College &amp; Research Institute, Thrissur (Christian Minority)</t>
+  </si>
+  <si>
+    <t>Kerala</t>
+  </si>
+  <si>
+    <t>Amala Institute of Medical Sciences, Thrissur (Christian Minority)</t>
+  </si>
+  <si>
+    <t>Pushpagiri Institute Of Medical Sciences and Research Centre, Tiruvalla (Christian Minority)</t>
+  </si>
+  <si>
+    <t>Malankara Orthodox Syrian Church Medical College, Kolenchery (Christian Minority)</t>
+  </si>
+  <si>
+    <t>Al-Ameen Medical College, Bijapur</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>Sree Gokulam Medical College Trust &amp; Research Foundation, Trivandrum</t>
+  </si>
+  <si>
+    <t>Believers Church Medical College Hospital, Thiruvalla, Kerala (Christian Minority)</t>
+  </si>
+  <si>
+    <t>Kempegowda Institute of Medical Sciences, Bangalore</t>
+  </si>
+  <si>
+    <t>Vydehi Institute of Medical Science and Research Centre, Bangalore</t>
+  </si>
+  <si>
+    <t>Father Muller Institute of Med. Education &amp; Research, Mangalore</t>
+  </si>
+  <si>
+    <t>M E S Medical College , Perintalmanna Malappuram Distt (Muslim Minority)</t>
+  </si>
+  <si>
+    <t>KMCT Medical College, Kozhikode, Calicut (Muslim Minority)</t>
+  </si>
+  <si>
+    <t>Travancore Medical College, Mylapore, Umayanalloor P O, Kollam (Muslim Minority)</t>
+  </si>
+  <si>
+    <t>Dr. Somervel Memorial CSI Hospital &amp; Medical College, Karakonam, Thiruvananthapuram (Christian Minority)</t>
+  </si>
+  <si>
+    <t>Sree Narayana Instt. of Medical Sciences, Chalakka, Ernakulam</t>
+  </si>
+  <si>
+    <t>SUT Sree Uthradom Thiurnal Academy of Medical Sciences, Trivandrum</t>
+  </si>
+  <si>
+    <t>BGS MEDICAL COLLAGE AND HOSPITAL,BANGALURU (Private-University)</t>
+  </si>
+  <si>
+    <t>Raipur Institute of Medical Sciences (RIMS), Raipur</t>
+  </si>
+  <si>
+    <t>Chhattisgarh</t>
+  </si>
+  <si>
+    <t>Dr. B.R. Ambedkar Medical College, Bangalore</t>
+  </si>
+  <si>
+    <t>Dr Moopens Medical College ,Meppadi P.O., Wayanad</t>
+  </si>
+  <si>
+    <t>Jaya Jagadguru Murugharajendra Medical College, Davangere</t>
+  </si>
+  <si>
+    <t>A.J.Institute of Medical Sciences &amp; Research Center, Mangalore</t>
+  </si>
+  <si>
+    <t>M.V.J.Medical College and Research Hospital, Bangalore</t>
+  </si>
+  <si>
+    <t>P K Das Institute of Medical Sciences, Palakkad, Kerala</t>
+  </si>
+  <si>
+    <t>Karuna Medical College, Palakkad</t>
+  </si>
+  <si>
+    <t>Shymanuru Shivashankarappa Institute Of Medical Sciences, Davangere</t>
+  </si>
+  <si>
+    <t>Mount Zion Medical College, Chayalode, Ezhamkulam Adoor, Pathanamthitta</t>
+  </si>
+  <si>
+    <t>Appolo Institute of Medical Sciences and Research, Hyderabad</t>
+  </si>
+  <si>
+    <t>Telangana</t>
+  </si>
+  <si>
+    <t>Palakkad Institute of Medical Sciences, Palakkad</t>
+  </si>
+  <si>
+    <t>Akash Institute of Medical Sciences &amp; Research centre, Banglore</t>
+  </si>
+  <si>
+    <t>The Oxford Medical College, Hospital &amp; Research Centre, Bangalore,(Linguistic Telugu )</t>
+  </si>
+  <si>
+    <t>Al-Azhar Medical College and Super Speciality Hospital, Thodupuzha (Muslim Minority)</t>
+  </si>
+  <si>
+    <t>Shri Balaji Institute of Medical Science, Raipur</t>
+  </si>
+  <si>
+    <t>Mahadevappa Rampure Medical College, Gulbarga</t>
+  </si>
+  <si>
+    <t>East Point College of Medical Sciences and Research Center, Bangalore</t>
+  </si>
+  <si>
+    <t>SIDDAGANGA MEDICAL COLLEGE AND RESEARCH INSTITUTE,,TUMAKURU</t>
+  </si>
+  <si>
+    <t>Deccan College of Medical Sciences, Hyderabad</t>
+  </si>
+  <si>
+    <t>S. Nijalingappa Medical College and Research Centre, Bagalkot</t>
+  </si>
+  <si>
+    <t>Mamata Academy of Medical Sciences, Bachupally</t>
+  </si>
+  <si>
+    <t>Kamineni Academy of Medical Sciences &amp; Research Centre, Hyderabad.</t>
+  </si>
+  <si>
+    <t>Bhaskar Medical College, Yenkapally,Hyderabad</t>
+  </si>
+  <si>
+    <t>Basaveshwara Medical College and Hospital, Chitradurga</t>
+  </si>
+  <si>
+    <t>Shadan Institute of Medical Sciences, Research Centre &amp;Teaching Hospital, Peerancheru, Hyderabad</t>
+  </si>
+  <si>
+    <t>Navodaya Medical College, Raichur</t>
+  </si>
+  <si>
+    <t>S R PATIL MEDICAL COLLEGE HOSPITAL AND RESEARCH CENTER,BADAGANDI,BAGALKOT</t>
+  </si>
+  <si>
+    <t>Subbaiah Institute of Medical Science, shimoga</t>
+  </si>
+  <si>
+    <t>SRI CHAMUNDESHWARI MEDICAL COLLEGE, HOSPITAL AND RESEARCH INST,,CHANNAPATNA, RAMANAGARA</t>
+  </si>
+  <si>
+    <t>M.S.Ramaiah Medical College, Bangalore (Private-University)</t>
+  </si>
+  <si>
+    <t>Abhishek I Mishra Memorial Medical College &amp; Research, Bhiali, Durg</t>
+  </si>
+  <si>
+    <t>SVS Medical College, Mehaboobnagar</t>
+  </si>
+  <si>
+    <t>Shridevi Institute of Medical Sciences &amp; Research Hospital, Tumkur</t>
+  </si>
+  <si>
+    <t>Kanachur Institute of Medical Sciences and Research Centre, Mangalore</t>
+  </si>
+  <si>
+    <t>Mamata Medical College, Khammam</t>
+  </si>
+  <si>
+    <t>Mediciti Institute of Medical Sciences, Ghanpur,Hyderabad</t>
+  </si>
+  <si>
+    <t>Maheswara Medical College, Chitkul, Patancheru, Medak</t>
+  </si>
+  <si>
+    <t>K.Venkataramana Gowda Medical College and Hospital, Mangalore</t>
+  </si>
+  <si>
+    <t>Prathima Institute of Medical Sciences, Karimnagar</t>
+  </si>
+  <si>
+    <t>RVM Institute of Medical sciences and Research Centre, Medak</t>
+  </si>
+  <si>
+    <t>Shri Rawatpura Sarkar Institute of Medical Sciences and Research, Nava Raipur</t>
+  </si>
+  <si>
+    <t>Mahavir Institute Of Medical Sciences, Vikarabad, Telengana</t>
+  </si>
+  <si>
+    <t>K.D. Medical College Hospital &amp; Research Centre, Mathura</t>
+  </si>
+  <si>
+    <t>Uttar Pradesh</t>
+  </si>
+  <si>
+    <t>Sri Madhusudan Sai Institute of Medical Sciences and Research, Chikballapur (Private-University)</t>
+  </si>
+  <si>
+    <t>Kamineni Institute of Medical Sciences, Narketpally.</t>
+  </si>
+  <si>
+    <t>SDM College of Medical Sciences and Hospital, Dharwad (Private-University)</t>
+  </si>
+  <si>
+    <t>Nova inst. Hayathnagar</t>
+  </si>
+  <si>
+    <t>Khaja Bande Navaz Institute Of Medical Sciences, Gulbarga (Private-University)</t>
+  </si>
+  <si>
+    <t>Pratima relif Warngal</t>
+  </si>
+  <si>
+    <t>TRR INSTITUTE OF MEDICAL SCIENCES, INOLE, PATANCHERU</t>
+  </si>
+  <si>
+    <t>Surabhi Institute of Medical Sciences, Siddipet, Telangana</t>
+  </si>
+  <si>
+    <t>FATHER COLOMBO INSTITUTE OF MEDICAL SCIENCES, WARANGAL</t>
+  </si>
+  <si>
+    <t>United Inst. Of Medical Science, Prayagraj</t>
+  </si>
+  <si>
+    <t>Hind Institute of Medical Sciences, Barabanki</t>
+  </si>
+  <si>
+    <t>Hind Institute of Medical Sciences, Sitapur</t>
+  </si>
+  <si>
+    <t>PES UNIVERSITY INSTITUTE OF MEDICAL SCIENCES AND RESEARCH,ELECTRONIC CITY,BANGALORE (Private-University)</t>
+  </si>
+  <si>
+    <t>Heritage Institute of Medical Sciences, Varanasi</t>
+  </si>
+  <si>
+    <t>Saraswati Institute of Medical Sciences, Hapur</t>
+  </si>
+  <si>
+    <t>School of Medical Sciences &amp; Research ( Sharda University),Greater Noida</t>
+  </si>
+  <si>
+    <t>Shri Gorakshnath Medical College, Hospital and Research Centre</t>
+  </si>
+  <si>
+    <t>Chalmeda Anand Rao Institute of Medical Science, Karimnagar.</t>
+  </si>
+  <si>
+    <t>MNR Medical College &amp; Hospital, Sangareddy</t>
+  </si>
+  <si>
+    <t>DR. CHANDRAMMA DAYANANDA SAGAR INSTITUTE OF MEDICAL EDUCATION &amp; RESEARCH,HAROHALLI.(Private-University)</t>
+  </si>
+  <si>
+    <t>Rama Medical College Hospital &amp; Research Centre, Hapur</t>
+  </si>
+  <si>
+    <t>Adichunchanagiri Institute of Medical Sciences, Mandya (Private-University)</t>
+  </si>
+  <si>
+    <t>NEELIMA INSTITUTE OF MEDICAL SCIENCES, GHATKESAR</t>
+  </si>
+  <si>
+    <t>Subharti Medical College, Meerut</t>
+  </si>
+  <si>
+    <t>Rama Medical College &amp; Hospital , Kanpur</t>
+  </si>
+  <si>
+    <t>Muzaffarnagar Medical College, Muzaffarnagar</t>
+  </si>
+  <si>
+    <t>Mayo Institute of Medical Sciences, Barabanki</t>
+  </si>
+  <si>
+    <t>National Capital Reagon Int. Of Medical Sci.,Meerut (MSY Medical College)</t>
+  </si>
+  <si>
+    <t>G.S Medical College, Hapur</t>
+  </si>
+  <si>
+    <t>Prasad Institute of Medical Sciences, Lucknow</t>
+  </si>
+  <si>
+    <t>S.K.S. HOSPITAL MATHURA</t>
+  </si>
+  <si>
+    <t>Sri Venkteshwara Inst.Of Medical Sci. Amroha</t>
+  </si>
+  <si>
+    <t>Ajay Sangaal Institute Of Medical Sciences &amp; Research</t>
+  </si>
+  <si>
+    <t>Narayana Medical College, Kanpur</t>
+  </si>
+  <si>
+    <t>Krishna Mohan Medical College &amp; Hospital, Mathura</t>
+  </si>
+  <si>
+    <t>Saraswati Medical College, Unnao</t>
+  </si>
+  <si>
+    <t>Shri Shankaracharya Institute of Medical Sciences, Bhilai</t>
+  </si>
+  <si>
+    <t>Dr BS Kushwah Institute of Medical Sciences</t>
+  </si>
+  <si>
+    <t>Noida INternational Inst. Of Med. Sci,Gautam Budh Nagar</t>
+  </si>
+  <si>
+    <t>Shri RamMurti Smarak Institute of Medical Sciences, Bareilly</t>
+  </si>
+  <si>
+    <t>Sapthagiri Institute of Medical Sciences, Bangalore (Private-University)</t>
+  </si>
+  <si>
+    <t>Varunarjun Medical College, Sahjahanpur</t>
+  </si>
+  <si>
+    <t>KMC Medical College &amp; Hospital Maharajganj</t>
+  </si>
+  <si>
+    <t>BGS Global Institute of Medical Sciences, Bangalore</t>
+  </si>
+  <si>
+    <t>Rohilkhand Medical College &amp; Hospital, Bareilly</t>
+  </si>
+  <si>
+    <t>Geetanjali Medical College &amp; Hospital,Udaipur</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
+  </si>
+  <si>
+    <t>Era Lucknow Medical College, Lucknow(Muslim Minority)</t>
+  </si>
+  <si>
+    <t>Srinivasa Institute of Medical Research Center, Mangalore</t>
+  </si>
+  <si>
+    <t>T.S Mishra Medical College &amp; Hospital, Lucknow</t>
+  </si>
+  <si>
+    <t>Rajshree Medical Research Institute, Barielly</t>
+  </si>
+  <si>
+    <t>Integral Institute of Medical Sciences &amp; Research, Lucknow(Muslim Minority)</t>
+  </si>
+  <si>
+    <t>F.H. Medical College &amp; Hospital, Firozabad, Agra(Muslim Minority)</t>
+  </si>
+  <si>
+    <t>Jaipur National University Institute of Medical Sciences and Resarch Centre, Jagatpura, Jaipur</t>
+  </si>
+  <si>
+    <t>Ananta Institute of Medical Sciences &amp; Research Centre, Rajsamand</t>
+  </si>
+  <si>
+    <t>American International Institute of Medical Sciences, Bedwas</t>
+  </si>
+  <si>
+    <t>National Institute of Medical Science &amp; Research, Jaipur</t>
+  </si>
+  <si>
+    <t>Teerthankar Mahaveer Medical College, Moradabad(Jain Minority)</t>
+  </si>
+  <si>
+    <t>Dr. S.S. Tantia Medical College, Hospital &amp; Research Centre Tantia University, Sri Ganganagar</t>
+  </si>
+  <si>
+    <t>Mahatma Gandhi Medical College and Hospital, Jaipur</t>
+  </si>
+  <si>
+    <t>Sudha Medical College, Via Jagpura, Jhalawar Road, Kota</t>
+  </si>
+  <si>
+    <t>JIET Medical College And Hospital, Village Mogra, Jodhpur</t>
+  </si>
+  <si>
+    <t>Pacific Institute of Medical Sciences, Umarda, Udaipur</t>
+  </si>
+  <si>
+    <t>Vyas Medical College &amp; Hospital, Pali Road Jodhpu</t>
+  </si>
+  <si>
+    <t>Pacific Medical College &amp; Hospital, Bhilo Ka Bedla, Udaipur</t>
+  </si>
+  <si>
+    <t>Career Institute of Medical Sciences &amp; hospital, Lucknow(Muslim Minority)</t>
+  </si>
+  <si>
+    <t>NRI Medical College, Chinnakakani</t>
+  </si>
+  <si>
+    <t>Andhra Pradesh</t>
+  </si>
+  <si>
+    <t>Narayana Medical College, Nellore</t>
+  </si>
+  <si>
+    <t>Apollo Institute of Medical Sciences and Research, Chittoor</t>
+  </si>
+  <si>
+    <t>Alluri Seetharama Raju Academy of Medical Sciences, Eluru</t>
+  </si>
+  <si>
+    <t>Dr. Pinnamaneni Siddhartha Institute of Medical Sciences, Gannavaram</t>
+  </si>
+  <si>
+    <t>GSL Medical College, Rajahmundry</t>
+  </si>
+  <si>
+    <t>NRI Institute of Medical Sciences, Visakhapatnam</t>
+  </si>
+  <si>
+    <t>Katuri Medical College and Hospital, Guntur</t>
+  </si>
+  <si>
+    <t>P.E.S. Institute of Medical Sciences and Research, Kuppam</t>
+  </si>
+  <si>
+    <t>Konasema Institute of Medical Sciences and Research Foundation, Amalapuram</t>
+  </si>
+  <si>
+    <t>Great Eastern Medical School and Hospital, Srikakulam</t>
+  </si>
+  <si>
+    <t>Viswabharathi Medical College, Kurnool</t>
+  </si>
+  <si>
+    <t>Sri Balaji Medical College Hospital &amp; Research Institute, Renigunta</t>
+  </si>
+  <si>
+    <t>Gayatri Vidya Parishad Inst. of Health Care and Medical Technology, Visakhapatnam</t>
+  </si>
+  <si>
+    <t>Santhiram Medical College, Nandyal</t>
+  </si>
+  <si>
+    <t>Maharaja Institute of Medical Sciences, Vizianagaram</t>
+  </si>
+  <si>
+    <t>Anna Gowri Medical College and Hospital, Parameshwaramangalam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="9">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -617,17 +1423,17 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -651,7 +1457,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -672,7 +1478,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -723,7 +1529,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -741,2045 +1547,2046 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D144"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="57.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="19.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="19.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="14.5555555555556" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2">
         <v>23923</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2">
         <v>530</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3">
         <v>27193</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3">
         <v>526</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4">
         <v>29857</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4">
         <v>522</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5">
         <v>30264</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5">
         <v>522</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6">
         <v>30886</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6">
         <v>470</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7">
         <v>32658</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7">
         <v>519</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8">
         <v>33265</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8">
         <v>518</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9">
         <v>39089</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9">
         <v>512</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10">
         <v>44842</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10">
         <v>507</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11">
         <v>46084</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11">
         <v>505</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12">
         <v>46597</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12">
         <v>504</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13">
         <v>47199</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13">
         <v>504</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14">
         <v>49834</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14">
         <v>502</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15">
         <v>51573</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15">
         <v>500</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16">
         <v>54489</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16">
         <v>498</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17">
         <v>54956</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17">
         <v>497</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18">
         <v>55581</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18">
         <v>497</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19">
         <v>56287</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19">
         <v>496</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20">
         <v>58632</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20">
         <v>494</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21">
         <v>62384</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21">
         <v>491</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22">
         <v>62634</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="D22">
         <v>491</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23">
         <v>62905</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23">
         <v>491</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24">
         <v>66832</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24">
         <v>488</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25">
         <v>67382</v>
       </c>
-      <c r="D25" s="0" t="n">
+      <c r="D25">
         <v>487</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26">
         <v>72225</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26">
         <v>484</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27">
         <v>73399</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27">
         <v>483</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28">
         <v>74284</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28">
         <v>482</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29">
         <v>74953</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29">
         <v>482</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30">
         <v>75560</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D30">
         <v>481</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31">
         <v>75588</v>
       </c>
-      <c r="D31" s="0" t="n">
+      <c r="D31">
         <v>481</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32">
         <v>75865</v>
       </c>
-      <c r="D32" s="0" t="n">
+      <c r="D32">
         <v>481</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33">
         <v>76138</v>
       </c>
-      <c r="D33" s="0" t="n">
+      <c r="D33">
         <v>481</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34">
         <v>77897</v>
       </c>
-      <c r="D34" s="0" t="n">
+      <c r="D34">
         <v>480</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35">
         <v>82414</v>
       </c>
-      <c r="D35" s="0" t="n">
+      <c r="D35">
         <v>476</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36">
         <v>82567</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36">
         <v>476</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37">
         <v>85450</v>
       </c>
-      <c r="D37" s="0" t="n">
+      <c r="D37">
         <v>474</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38">
         <v>88406</v>
       </c>
-      <c r="D38" s="0" t="n">
+      <c r="D38">
         <v>472</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39">
         <v>89091</v>
       </c>
-      <c r="D39" s="0" t="n">
+      <c r="D39">
         <v>472</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40">
         <v>89719</v>
       </c>
-      <c r="D40" s="0" t="n">
+      <c r="D40">
         <v>471</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41">
         <v>91633</v>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D41">
         <v>470</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="0" t="n">
+      <c r="C42">
         <v>92154</v>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42">
         <v>470</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="0" t="n">
+      <c r="C43">
         <v>95359</v>
       </c>
-      <c r="D43" s="0" t="n">
+      <c r="D43">
         <v>467</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44">
         <v>95727</v>
       </c>
-      <c r="D44" s="0" t="n">
+      <c r="D44">
         <v>467</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="0" t="n">
+      <c r="C45">
         <v>98147</v>
       </c>
-      <c r="D45" s="0" t="n">
+      <c r="D45">
         <v>465</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="0" t="n">
+      <c r="C46">
         <v>101411</v>
       </c>
-      <c r="D46" s="0" t="n">
+      <c r="D46">
         <v>463</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="0" t="n">
+      <c r="C47">
         <v>102349</v>
       </c>
-      <c r="D47" s="0" t="n">
+      <c r="D47">
         <v>463</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48">
         <v>103870</v>
       </c>
-      <c r="D48" s="0" t="n">
+      <c r="D48">
         <v>462</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="0" t="n">
+      <c r="C49">
         <v>105378</v>
       </c>
-      <c r="D49" s="0" t="n">
+      <c r="D49">
         <v>461</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50">
         <v>105644</v>
       </c>
-      <c r="D50" s="0" t="n">
+      <c r="D50">
         <v>460</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" t="s">
         <v>35</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51">
         <v>106547</v>
       </c>
-      <c r="D51" s="0" t="n">
+      <c r="D51">
         <v>460</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" t="s">
         <v>10</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52">
         <v>108184</v>
       </c>
-      <c r="D52" s="0" t="n">
+      <c r="D52">
         <v>459</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
         <v>59</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" t="s">
         <v>10</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53">
         <v>109071</v>
       </c>
-      <c r="D53" s="0" t="n">
+      <c r="D53">
         <v>458</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
         <v>60</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="0" t="n">
+      <c r="C54">
         <v>111791</v>
       </c>
-      <c r="D54" s="0" t="n">
+      <c r="D54">
         <v>456</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" t="s">
         <v>35</v>
       </c>
-      <c r="C55" s="0" t="n">
+      <c r="C55">
         <v>112920</v>
       </c>
-      <c r="D55" s="0" t="n">
+      <c r="D55">
         <v>456</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" t="s">
         <v>35</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56">
         <v>115427</v>
       </c>
-      <c r="D56" s="0" t="n">
+      <c r="D56">
         <v>454</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
         <v>63</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="0" t="n">
+      <c r="C57">
         <v>117899</v>
       </c>
-      <c r="D57" s="0" t="n">
+      <c r="D57">
         <v>453</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" t="s">
         <v>35</v>
       </c>
-      <c r="C58" s="0" t="n">
+      <c r="C58">
         <v>119298</v>
       </c>
-      <c r="D58" s="0" t="n">
+      <c r="D58">
         <v>452</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" t="s">
         <v>35</v>
       </c>
-      <c r="C59" s="0" t="n">
+      <c r="C59">
         <v>121662</v>
       </c>
-      <c r="D59" s="0" t="n">
+      <c r="D59">
         <v>450</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="0" t="n">
+      <c r="C60">
         <v>122070</v>
       </c>
-      <c r="D60" s="0" t="n">
+      <c r="D60">
         <v>450</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" t="s">
         <v>35</v>
       </c>
-      <c r="C61" s="0" t="n">
+      <c r="C61">
         <v>124954</v>
       </c>
-      <c r="D61" s="0" t="n">
+      <c r="D61">
         <v>448</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
         <v>68</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" t="s">
         <v>69</v>
       </c>
-      <c r="C62" s="0" t="n">
+      <c r="C62">
         <v>132349</v>
       </c>
-      <c r="D62" s="0" t="n">
+      <c r="D62">
         <v>444</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
         <v>70</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="0" t="n">
+      <c r="C63">
         <v>133279</v>
       </c>
-      <c r="D63" s="0" t="n">
+      <c r="D63">
         <v>443</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
         <v>71</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" t="s">
         <v>35</v>
       </c>
-      <c r="C64" s="0" t="n">
+      <c r="C64">
         <v>134490</v>
       </c>
-      <c r="D64" s="0" t="n">
+      <c r="D64">
         <v>442</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
         <v>72</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="0" t="n">
+      <c r="C65">
         <v>134706</v>
       </c>
-      <c r="D65" s="0" t="n">
+      <c r="D65">
         <v>442</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" t="s">
         <v>35</v>
       </c>
-      <c r="C66" s="0" t="n">
+      <c r="C66">
         <v>137567</v>
       </c>
-      <c r="D66" s="0" t="n">
+      <c r="D66">
         <v>440</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
         <v>74</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" t="s">
         <v>10</v>
       </c>
-      <c r="C67" s="0" t="n">
+      <c r="C67">
         <v>137867</v>
       </c>
-      <c r="D67" s="0" t="n">
+      <c r="D67">
         <v>440</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
         <v>75</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" t="s">
         <v>35</v>
       </c>
-      <c r="C68" s="0" t="n">
+      <c r="C68">
         <v>140042</v>
       </c>
-      <c r="D68" s="0" t="n">
+      <c r="D68">
         <v>439</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" t="s">
         <v>35</v>
       </c>
-      <c r="C69" s="0" t="n">
+      <c r="C69">
         <v>142644</v>
       </c>
-      <c r="D69" s="0" t="n">
+      <c r="D69">
         <v>437</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
         <v>77</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" t="s">
         <v>35</v>
       </c>
-      <c r="C70" s="0" t="n">
+      <c r="C70">
         <v>143528</v>
       </c>
-      <c r="D70" s="0" t="n">
+      <c r="D70">
         <v>437</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
         <v>78</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" t="s">
         <v>35</v>
       </c>
-      <c r="C71" s="0" t="n">
+      <c r="C71">
         <v>144275</v>
       </c>
-      <c r="D71" s="0" t="n">
+      <c r="D71">
         <v>436</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="0" t="n">
+      <c r="C72">
         <v>153216</v>
       </c>
-      <c r="D72" s="0" t="n">
+      <c r="D72">
         <v>431</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" t="s">
         <v>69</v>
       </c>
-      <c r="C73" s="0" t="n">
+      <c r="C73">
         <v>160036</v>
       </c>
-      <c r="D73" s="0" t="n">
+      <c r="D73">
         <v>427</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
         <v>81</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" t="s">
         <v>69</v>
       </c>
-      <c r="C74" s="0" t="n">
+      <c r="C74">
         <v>160036</v>
       </c>
-      <c r="D74" s="0" t="n">
+      <c r="D74">
         <v>427</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
         <v>82</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="0" t="n">
+      <c r="C75">
         <v>171713</v>
       </c>
-      <c r="D75" s="0" t="n">
+      <c r="D75">
         <v>421</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
         <v>83</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" t="s">
         <v>69</v>
       </c>
-      <c r="C76" s="0" t="n">
+      <c r="C76">
         <v>189181</v>
       </c>
-      <c r="D76" s="0" t="n">
+      <c r="D76">
         <v>411</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" t="s">
         <v>69</v>
       </c>
-      <c r="C77" s="0" t="n">
+      <c r="C77">
         <v>190852</v>
       </c>
-      <c r="D77" s="0" t="n">
+      <c r="D77">
         <v>410</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" t="s">
         <v>69</v>
       </c>
-      <c r="C78" s="0" t="n">
+      <c r="C78">
         <v>195896</v>
       </c>
-      <c r="D78" s="0" t="n">
+      <c r="D78">
         <v>408</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
         <v>86</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" t="s">
         <v>69</v>
       </c>
-      <c r="C79" s="0" t="n">
+      <c r="C79">
         <v>196805</v>
       </c>
-      <c r="D79" s="0" t="n">
+      <c r="D79">
         <v>407</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
         <v>87</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" t="s">
         <v>35</v>
       </c>
-      <c r="C80" s="0" t="n">
+      <c r="C80">
         <v>197567</v>
       </c>
-      <c r="D80" s="0" t="n">
+      <c r="D80">
         <v>440</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
         <v>88</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" t="s">
         <v>35</v>
       </c>
-      <c r="C81" s="0" t="n">
+      <c r="C81">
         <v>197567</v>
       </c>
-      <c r="D81" s="0" t="n">
+      <c r="D81">
         <v>440</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
         <v>89</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" t="s">
         <v>10</v>
       </c>
-      <c r="C82" s="0" t="n">
+      <c r="C82">
         <v>212337</v>
       </c>
-      <c r="D82" s="0" t="n">
+      <c r="D82">
         <v>399</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
         <v>90</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" t="s">
         <v>69</v>
       </c>
-      <c r="C83" s="0" t="n">
+      <c r="C83">
         <v>229989</v>
       </c>
-      <c r="D83" s="0" t="n">
+      <c r="D83">
         <v>390</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
         <v>91</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="0" t="n">
+      <c r="C84">
         <v>234085</v>
       </c>
-      <c r="D84" s="0" t="n">
+      <c r="D84">
         <v>388</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
         <v>92</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" t="s">
         <v>35</v>
       </c>
-      <c r="C85" s="0" t="n">
+      <c r="C85">
         <v>244556</v>
       </c>
-      <c r="D85" s="0" t="n">
+      <c r="D85">
         <v>383</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
         <v>93</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" t="s">
         <v>69</v>
       </c>
-      <c r="C86" s="0" t="n">
+      <c r="C86">
         <v>266476</v>
       </c>
-      <c r="D86" s="0" t="n">
+      <c r="D86">
         <v>372</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
         <v>94</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" t="s">
         <v>69</v>
       </c>
-      <c r="C87" s="0" t="n">
+      <c r="C87">
         <v>269532</v>
       </c>
-      <c r="D87" s="0" t="n">
+      <c r="D87">
         <v>371</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" t="s">
         <v>69</v>
       </c>
-      <c r="C88" s="0" t="n">
+      <c r="C88">
         <v>296410</v>
       </c>
-      <c r="D88" s="0" t="n">
+      <c r="D88">
         <v>359</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
         <v>96</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" t="s">
         <v>69</v>
       </c>
-      <c r="C89" s="0" t="n">
+      <c r="C89">
         <v>334849</v>
       </c>
-      <c r="D89" s="0" t="n">
+      <c r="D89">
         <v>342</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
         <v>97</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" t="s">
         <v>69</v>
       </c>
-      <c r="C90" s="0" t="n">
+      <c r="C90">
         <v>336679</v>
       </c>
-      <c r="D90" s="0" t="n">
+      <c r="D90">
         <v>341</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
         <v>98</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" t="s">
         <v>69</v>
       </c>
-      <c r="C91" s="0" t="n">
+      <c r="C91">
         <v>351380</v>
       </c>
-      <c r="D91" s="0" t="n">
+      <c r="D91">
         <v>335</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
         <v>99</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" t="s">
         <v>69</v>
       </c>
-      <c r="C92" s="0" t="n">
+      <c r="C92">
         <v>357901</v>
       </c>
-      <c r="D92" s="0" t="n">
+      <c r="D92">
         <v>332</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
         <v>100</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" t="s">
         <v>69</v>
       </c>
-      <c r="C93" s="0" t="n">
+      <c r="C93">
         <v>364468</v>
       </c>
-      <c r="D93" s="0" t="n">
+      <c r="D93">
         <v>330</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
         <v>101</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" t="s">
         <v>69</v>
       </c>
-      <c r="C94" s="0" t="n">
+      <c r="C94">
         <v>375194</v>
       </c>
-      <c r="D94" s="0" t="n">
+      <c r="D94">
         <v>325</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
         <v>102</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" t="s">
         <v>69</v>
       </c>
-      <c r="C95" s="0" t="n">
+      <c r="C95">
         <v>382152</v>
       </c>
-      <c r="D95" s="0" t="n">
+      <c r="D95">
         <v>323</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
         <v>103</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" t="s">
         <v>69</v>
       </c>
-      <c r="C96" s="0" t="n">
+      <c r="C96">
         <v>383586</v>
       </c>
-      <c r="D96" s="0" t="n">
+      <c r="D96">
         <v>322</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
         <v>104</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" t="s">
         <v>69</v>
       </c>
-      <c r="C97" s="0" t="n">
+      <c r="C97">
         <v>392077</v>
       </c>
-      <c r="D97" s="0" t="n">
+      <c r="D97">
         <v>319</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
         <v>105</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" t="s">
         <v>69</v>
       </c>
-      <c r="C98" s="0" t="n">
+      <c r="C98">
         <v>402286</v>
       </c>
-      <c r="D98" s="0" t="n">
+      <c r="D98">
         <v>315</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
         <v>106</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" t="s">
         <v>24</v>
       </c>
-      <c r="C99" s="0" t="n">
+      <c r="C99">
         <v>404611</v>
       </c>
-      <c r="D99" s="0" t="n">
+      <c r="D99">
         <v>314</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
         <v>107</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" t="s">
         <v>69</v>
       </c>
-      <c r="C100" s="0" t="n">
+      <c r="C100">
         <v>421396</v>
       </c>
-      <c r="D100" s="0" t="n">
+      <c r="D100">
         <v>308</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
         <v>108</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" t="s">
         <v>69</v>
       </c>
-      <c r="C101" s="0" t="n">
+      <c r="C101">
         <v>427750</v>
       </c>
-      <c r="D101" s="0" t="n">
+      <c r="D101">
         <v>305</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
         <v>109</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" t="s">
         <v>69</v>
       </c>
-      <c r="C102" s="0" t="n">
+      <c r="C102">
         <v>433125</v>
       </c>
-      <c r="D102" s="0" t="n">
+      <c r="D102">
         <v>304</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
         <v>110</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="0" t="n">
+      <c r="C103">
         <v>436705</v>
       </c>
-      <c r="D103" s="0" t="n">
+      <c r="D103">
         <v>302</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
         <v>111</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" t="s">
         <v>69</v>
       </c>
-      <c r="C104" s="0" t="n">
+      <c r="C104">
         <v>439268</v>
       </c>
-      <c r="D104" s="0" t="n">
+      <c r="D104">
         <v>301</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
         <v>112</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" t="s">
         <v>69</v>
       </c>
-      <c r="C105" s="0" t="n">
+      <c r="C105">
         <v>440266</v>
       </c>
-      <c r="D105" s="0" t="n">
+      <c r="D105">
         <v>301</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
         <v>113</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="0" t="n">
+      <c r="C106">
         <v>445758</v>
       </c>
-      <c r="D106" s="0" t="n">
+      <c r="D106">
         <v>299</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
         <v>114</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" t="s">
         <v>69</v>
       </c>
-      <c r="C107" s="0" t="n">
+      <c r="C107">
         <v>500475</v>
       </c>
-      <c r="D107" s="0" t="n">
+      <c r="D107">
         <v>281</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
         <v>115</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" t="s">
         <v>116</v>
       </c>
-      <c r="C108" s="0" t="n">
+      <c r="C108">
         <v>558179</v>
       </c>
-      <c r="D108" s="0" t="n">
+      <c r="D108">
         <v>263</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
         <v>117</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" t="s">
         <v>69</v>
       </c>
-      <c r="C109" s="0" t="n">
+      <c r="C109">
         <v>580210</v>
       </c>
-      <c r="D109" s="0" t="n">
+      <c r="D109">
         <v>255</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
         <v>118</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" t="s">
         <v>10</v>
       </c>
-      <c r="C110" s="0" t="n">
+      <c r="C110">
         <v>581641</v>
       </c>
-      <c r="D110" s="0" t="n">
+      <c r="D110">
         <v>256</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
         <v>119</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" t="s">
         <v>69</v>
       </c>
-      <c r="C111" s="0" t="n">
+      <c r="C111">
         <v>591567</v>
       </c>
-      <c r="D111" s="0" t="n">
+      <c r="D111">
         <v>253</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
         <v>120</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" t="s">
         <v>69</v>
       </c>
-      <c r="C112" s="0" t="n">
+      <c r="C112">
         <v>600891</v>
       </c>
-      <c r="D112" s="0" t="n">
+      <c r="D112">
         <v>250</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
         <v>121</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" t="s">
         <v>69</v>
       </c>
-      <c r="C113" s="0" t="n">
+      <c r="C113">
         <v>628502</v>
       </c>
-      <c r="D113" s="0" t="n">
+      <c r="D113">
         <v>242</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
         <v>122</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" t="s">
         <v>69</v>
       </c>
-      <c r="C114" s="0" t="n">
+      <c r="C114">
         <v>722941</v>
       </c>
-      <c r="D114" s="0" t="n">
+      <c r="D114">
         <v>218</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
         <v>123</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" t="s">
         <v>116</v>
       </c>
-      <c r="C115" s="0" t="n">
+      <c r="C115">
         <v>911481</v>
       </c>
-      <c r="D115" s="0" t="n">
+      <c r="D115">
         <v>177</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
         <v>124</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" t="s">
         <v>116</v>
       </c>
-      <c r="C116" s="0" t="n">
+      <c r="C116">
         <v>919665</v>
       </c>
-      <c r="D116" s="0" t="n">
+      <c r="D116">
         <v>176</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
         <v>125</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="0" t="n">
+      <c r="C117">
         <v>1001133</v>
       </c>
-      <c r="D117" s="0" t="n">
+      <c r="D117">
         <v>160</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
         <v>126</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" t="s">
         <v>116</v>
       </c>
-      <c r="C118" s="0" t="n">
+      <c r="C118">
         <v>1076504</v>
       </c>
-      <c r="D118" s="0" t="n">
+      <c r="D118">
         <v>147</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
         <v>127</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" t="s">
         <v>69</v>
       </c>
-      <c r="C119" s="0" t="n">
+      <c r="C119">
         <v>1085133</v>
       </c>
-      <c r="D119" s="0" t="n">
+      <c r="D119">
         <v>146</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
         <v>128</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" t="s">
         <v>116</v>
       </c>
-      <c r="C120" s="0" t="n">
+      <c r="C120">
         <v>1117630</v>
       </c>
-      <c r="D120" s="0" t="n">
+      <c r="D120">
         <v>141</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
         <v>129</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" t="s">
         <v>116</v>
       </c>
-      <c r="C121" s="0" t="n">
+      <c r="C121">
         <v>1267561</v>
       </c>
-      <c r="D121" s="0" t="n">
+      <c r="D121">
         <v>119</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
         <v>130</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" t="s">
         <v>116</v>
       </c>
-      <c r="C122" s="0" t="n">
+      <c r="C122">
         <v>1268204</v>
       </c>
-      <c r="D122" s="0" t="n">
+      <c r="D122">
         <v>119</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
         <v>131</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" t="s">
         <v>116</v>
       </c>
-      <c r="C123" s="0" t="n">
+      <c r="C123">
         <v>1291243</v>
       </c>
-      <c r="D123" s="0" t="n">
+      <c r="D123">
         <v>166</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
         <v>132</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" t="s">
         <v>116</v>
       </c>
-      <c r="C124" s="0" t="n">
+      <c r="C124">
         <v>1296229</v>
       </c>
-      <c r="D124" s="0" t="n">
+      <c r="D124">
         <v>116</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
         <v>133</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" t="s">
         <v>116</v>
       </c>
-      <c r="C125" s="0" t="n">
+      <c r="C125">
         <v>1307816</v>
       </c>
-      <c r="D125" s="0" t="n">
+      <c r="D125">
         <v>115</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
         <v>134</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" t="s">
         <v>116</v>
       </c>
-      <c r="C126" s="0" t="n">
+      <c r="C126">
         <v>1314408</v>
       </c>
-      <c r="D126" s="0" t="n">
+      <c r="D126">
         <v>113</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
         <v>135</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" t="s">
         <v>69</v>
       </c>
-      <c r="C127" s="0" t="n">
+      <c r="C127">
         <v>6699854</v>
       </c>
-      <c r="D127" s="0" t="n">
+      <c r="D127">
         <v>231</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
         <v>136</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" t="s">
         <v>137</v>
       </c>
-      <c r="C128" s="0" t="n">
+      <c r="C128">
         <v>143044</v>
       </c>
-      <c r="D128" s="0" t="n">
+      <c r="D128">
         <v>437</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
         <v>138</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" t="s">
         <v>137</v>
       </c>
-      <c r="C129" s="0" t="n">
+      <c r="C129">
         <v>127250</v>
       </c>
-      <c r="D129" s="0" t="n">
+      <c r="D129">
         <v>447</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
         <v>139</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" t="s">
         <v>137</v>
       </c>
-      <c r="C130" s="0" t="n">
+      <c r="C130">
         <v>116095</v>
       </c>
-      <c r="D130" s="0" t="n">
+      <c r="D130">
         <v>454</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
         <v>140</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" t="s">
         <v>137</v>
       </c>
-      <c r="C131" s="0" t="n">
+      <c r="C131">
         <v>154843</v>
       </c>
-      <c r="D131" s="0" t="n">
+      <c r="D131">
         <v>430</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
         <v>141</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" t="s">
         <v>137</v>
       </c>
-      <c r="C132" s="0" t="n">
+      <c r="C132">
         <v>150084</v>
       </c>
-      <c r="D132" s="0" t="n">
+      <c r="D132">
         <v>433</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
         <v>142</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" t="s">
         <v>137</v>
       </c>
-      <c r="C133" s="0" t="n">
+      <c r="C133">
         <v>189662</v>
       </c>
-      <c r="D133" s="0" t="n">
+      <c r="D133">
         <v>411</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="s">
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
         <v>143</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" t="s">
         <v>137</v>
       </c>
-      <c r="C134" s="0" t="n">
+      <c r="C134">
         <v>235044</v>
       </c>
-      <c r="D134" s="0" t="n">
+      <c r="D134">
         <v>387</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
         <v>144</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" t="s">
         <v>137</v>
       </c>
-      <c r="C135" s="0" t="n">
+      <c r="C135">
         <v>199997</v>
       </c>
-      <c r="D135" s="0" t="n">
+      <c r="D135">
         <v>405</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="s">
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
         <v>145</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" t="s">
         <v>137</v>
       </c>
-      <c r="C136" s="0" t="n">
+      <c r="C136">
         <v>122664</v>
       </c>
-      <c r="D136" s="0" t="n">
+      <c r="D136">
         <v>450</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="s">
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
         <v>146</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" t="s">
         <v>137</v>
       </c>
-      <c r="C137" s="0" t="n">
+      <c r="C137">
         <v>204510</v>
       </c>
-      <c r="D137" s="0" t="n">
+      <c r="D137">
         <v>403</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="s">
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
         <v>147</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="B138" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="0" t="n">
+      <c r="C138">
         <v>165521</v>
       </c>
-      <c r="D138" s="0" t="n">
+      <c r="D138">
         <v>424</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="s">
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
         <v>148</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" t="s">
         <v>137</v>
       </c>
-      <c r="C139" s="0" t="n">
+      <c r="C139">
         <v>245870</v>
       </c>
-      <c r="D139" s="0" t="n">
+      <c r="D139">
         <v>382</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="s">
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
         <v>149</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" t="s">
         <v>137</v>
       </c>
-      <c r="C140" s="0" t="n">
+      <c r="C140">
         <v>223925</v>
       </c>
-      <c r="D140" s="0" t="n">
+      <c r="D140">
         <v>393</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0" t="s">
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
         <v>150</v>
       </c>
-      <c r="B141" s="0" t="s">
+      <c r="B141" t="s">
         <v>137</v>
       </c>
-      <c r="C141" s="0" t="n">
+      <c r="C141">
         <v>160073</v>
       </c>
-      <c r="D141" s="0" t="n">
+      <c r="D141">
         <v>427</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0" t="s">
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
         <v>151</v>
       </c>
-      <c r="B142" s="0" t="s">
+      <c r="B142" t="s">
         <v>137</v>
       </c>
-      <c r="C142" s="0" t="n">
+      <c r="C142">
         <v>193664</v>
       </c>
-      <c r="D142" s="0" t="n">
+      <c r="D142">
         <v>409</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="s">
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
         <v>152</v>
       </c>
-      <c r="B143" s="0" t="s">
+      <c r="B143" t="s">
         <v>137</v>
       </c>
-      <c r="C143" s="0" t="n">
+      <c r="C143">
         <v>200955</v>
       </c>
-      <c r="D143" s="0" t="n">
+      <c r="D143">
         <v>405</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0" t="s">
+    <row r="144" spans="1:4">
+      <c r="A144" t="s">
         <v>153</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="B144" t="s">
         <v>137</v>
       </c>
-      <c r="C144" s="0" t="n">
+      <c r="C144">
         <v>342303</v>
       </c>
-      <c r="D144" s="0" t="n">
+      <c r="D144">
         <v>339</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>